--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -646,7 +646,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -740,7 +740,7 @@
     <t>MedicationDispense.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -872,7 +872,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>調剤が実行されなかった理由</t>
@@ -887,7 +887,7 @@
     <t>ディスペンスが実行されなかった理由を説明するコード。 / A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -911,7 +911,7 @@
     <t>分配された薬がどこで消費または投与されると予想されるコード。 / A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -921,7 +921,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication)</t>
+Reference(Medication|4.0.1)</t>
   </si>
   <si>
     <t>医薬品</t>
@@ -941,7 +941,7 @@
     <t>どの物質または製品を分配できるかを特定するコード化された概念。 / A coded concept identifying which substance or product can be dispensed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1009,7 +1009,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1083,7 +1083,7 @@
     <t>個人が薬物療法を調剤する上で果たした役割を説明するコード。 / A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1096,10 +1096,10 @@
 </t>
   </si>
   <si>
-    <t>演奏していた個人 / Individual who was performing</t>
-  </si>
-  <si>
-    <t>アクションを実行したデバイス、開業医など。俳優は薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
+    <t>調剤をした個人 / Individual who was performing</t>
+  </si>
+  <si>
+    <t>アクションを実行したデバイス、個人など。調剤した薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1127,7 +1127,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1461,7 +1461,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -1801,17 +1801,17 @@
   <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.12109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.3125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.2578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="246.64453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="211.453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1820,26 +1820,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="197.484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="169.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="62.83984375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
